--- a/artfynd/A 63029-2021 artfynd.xlsx
+++ b/artfynd/A 63029-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63029-2021 artfynd.xlsx
+++ b/artfynd/A 63029-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>72115364</v>
       </c>
       <c r="B2" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641991.9611194604</v>
+        <v>641992</v>
       </c>
       <c r="R2" t="n">
-        <v>6523201.667856201</v>
+        <v>6523202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -798,6 +793,242 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>98320307</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57563</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gråtrut</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Larus argentatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yttre Hållsfjärden, V Askö, Srm 6647 m W, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>641970</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6523330</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västerljung</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-01-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-01-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72115312</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>vägrenen, Viksfjärden, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>641992</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6523202</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västerljung</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-07-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-07-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Karlsson, Jan Gustafsson, Björn Erixon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63029-2021 artfynd.xlsx
+++ b/artfynd/A 63029-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72115364</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98320307</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72115312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>